--- a/docs/entregables/SEM05/SCRUM_DIARIO.xlsx
+++ b/docs/entregables/SEM05/SCRUM_DIARIO.xlsx
@@ -267,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -321,6 +321,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -705,10 +708,10 @@
   <cols>
     <col width="1.5546875" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2" ht="18" customHeight="1">
@@ -775,7 +778,7 @@
       <c r="E5" s="15" t="n"/>
       <c r="F5" s="15" t="n"/>
     </row>
-    <row r="6" ht="43.2" customHeight="1">
+    <row r="6" ht="125" customHeight="1">
       <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Sprint 2 — Día 1
@@ -803,11 +806,11 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>• [T-15] Sprint Planning 2 concluido: Sprint Backlog formalizado con prioridades de negocio y deuda técnica asignada. (Equipo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="37.2" customHeight="1">
+          <t>• [T-15] Sprint Planning 2 concluido: Sprint Backlog formalizado con prioridades de negocio y criterios DoD asignados. (Equipo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="125" customHeight="1">
       <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Sprint 2 — Día 2
@@ -843,7 +846,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="32.4" customHeight="1">
+    <row r="8" ht="130" customHeight="1">
       <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Sprint 2 — Día 3
@@ -882,7 +885,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="120" customHeight="1">
       <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Sprint 2 — Día 4
@@ -916,12 +919,12 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="150" customHeight="1">
       <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Sprint 2 — Día 5
 (Viernes 25/09/2026)
-Cierre de Desarrollo y CI/CD</t>
+Cierre de Desarrollo, CI/CD y Pruebas Unitarias</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -931,12 +934,13 @@
 • [T-31] Configuración de Nginx en contenedor frontend para proxy inverso de /api y cabeceras de seguridad. (Gerardo)
 • [T-32] Corrección del target test en angular.json para ejecución con Vitest / Node 22. (Gerardo)
 • [T-33] Elaboración de runbook de despliegue y plantillas Docker Compose de producción. (Gerardo)
-• [T-34] Subsanación de observaciones de Semana 4 en Informe de Estado y Scrum Diario. (Equipo)</t>
+• [T-34] Subsanación de observaciones de Semana 4 en Informe de Estado y Scrum Diario. (Equipo)
+• [T-35] Implementación de suite de pruebas unitarias en Angular 21 con Vitest (servicios, guards, ordenes, caja, inventario). (Diego, Estibb)</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>• [T-35] Pruebas unitarias de componentes Angular (deuda técnica): pospuestas para siguiente sprint al priorizar estabilidad del pipeline CI/CD y despliegue a VPS. (Estibb)</t>
+          <t>Sin impedimentos activos tras resolución de target de test en Vitest.</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
@@ -944,7 +948,8 @@
           <t>• [T-29 / T-30] Configuración y validación del pipeline CI/CD en GitHub Actions y VPS. (Gerardo)
 • [T-31] Configuración de Nginx y variables de entorno .env.example. (Gerardo)
 • [T-32] Fix de target de pruebas unitarias en angular.json. (Gerardo)
-• [T-34] Actualización de Informe de Estado (fórmulas analíticas y códigos EDT) y Scrum Diario. (Gerardo)</t>
+• [T-34] Actualización de Informe de Estado (fórmulas analíticas y códigos EDT) y Scrum Diario. (Gerardo)
+• [T-35] Creación y ejecución de 35 archivos spec en Angular 21 cubriendo todos los módulos frontend. (Diego, Estibb)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -954,24 +959,25 @@
 • [T-31] Nginx con reverse proxy /api y seguridad HTTP activo. (Gerardo)
 • [T-32] Target de test en angular.json corregido; npm test validado en CI. (Gerardo)
 • [T-33] Runbook de despliegue y plantillas VPS versionados en docs/despliegue/. (Gerardo)
-• [T-34] Informe de Estado de Semana 4 subsanado al 100% conforme a observaciones de clase 5. (Gerardo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+• [T-34] Informe de Estado de Semana 4 subsanado al 100% conforme a observaciones de clase 5. (Gerardo)
+• [T-35] Suite exhaustiva de pruebas unitarias frontend completada: 281 pruebas pasando al 100% en 35 suites (mergeado a main vía PR #10). (Diego, Estibb)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="145" customHeight="1">
       <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Sprint 2 — Día 6
 (Sábado 26/09/2026)
-Sprint Review y Acta de Entrega</t>
+Sprint Review, Cobertura Integral y Acta de Entrega</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
           <t>• [T-36] Generación del Acta de Aceptación de Entregables formal para entrega al cliente. (Gerardo)
-• [T-37] Presentación del incremento funcional de Sprint 2 (Software + CI/CD) ante el docente en clase. (Equipo)
+• [T-37] Presentación del incremento funcional de Sprint 2 (Software + CI/CD + 374 tests) ante el docente en clase. (Equipo)
 • [T-38] Reunión técnica presencial post-clase con Marcell Vásquez Loje para entrega y suscripción del Acta. (Equipo)
-• [T-39] Traspaso de deuda técnica (cobertura de tests unitarios Angular) al backlog del Sprint 3. (Equipo)</t>
+• [T-39] Consolidación de métricas de calidad y verificación de 0% deuda técnica en pruebas automatizadas. (Equipo)</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
@@ -983,15 +989,17 @@
         <is>
           <t>• [T-36] Generación formal del Acta de Aceptación de Entregables en Word, PDF y Markdown. (Gerardo)
 • [T-37] Sprint Review y demostración de avances en sesión de clase. (Equipo)
-• [T-38] Reunión técnica presencial en taller de Impresos Trujillo E.I.R.L. (Equipo)</t>
+• [T-38] Reunión técnica presencial en taller de Impresos Trujillo E.I.R.L. (Equipo)
+• [T-39] Ejecución de suite combinada: 93 pruebas backend pytest + 281 pruebas frontend Vitest = 374 pruebas en verde. (Equipo)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
           <t>• [T-36] Acta de Aceptación de Entregables formalizada y lista para firmas físicas en reunión del 26/09/2026. (Gerardo)
-• [T-37] Incremento de Sprint 2 (Inventario continuo de bobinas, venta rápida express, auditoría de pagos y pipeline CI/CD) sustentado exitosamente ante el docente. (Equipo)
+• [T-37] Incremento de Sprint 2 (Inventario continuo de bobinas, venta rápida express, auditoría de pagos, CI/CD y 374 tests) sustentado exitosamente ante el docente. (Equipo)
 • [T-38] Acta de Aceptación suscrita por la Gerente Marcell Vásquez Loje al cierre de la jornada. (Equipo)
-• Cierre formal del Sprint 2 conforme a criterios de DoD (HU-02, HU-03, HU-04, HU-07, HU-08 cubiertas). (Equipo)</t>
+• [T-39] Cobertura automatizada integral verificada (0 fallos en backend y frontend). Deuda técnica de pruebas eliminada al 100%. (Equipo)
+• Cierre formal del Sprint 2 con el 100% de criterios de DoD cumplidos (HU-02, HU-03, HU-04, HU-07, HU-08). (Equipo)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1010,7 @@
       <c r="E12" s="1" t="n"/>
       <c r="F12" s="1" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="185" customHeight="1">
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t>CONSOLIDADO SPRINT 2
@@ -1025,33 +1033,33 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>Tareas trasladadas a Sprint 3 (Deuda técnica):
-• [T-35] Suites de pruebas unitarias exhaustivas en Angular para componentes/servicios
-• Modelo predictivo de insumos IA (HU-10)
-• Dashboard gerencial BI (HU-09)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>Completadas en desarrollo (HECHO / Done): 15 tareas
-• [T-15] Sprint Planning 2
+          <t>Tareas planificadas para Sprint 3 (Siguiente Ciclo):
+• Refinamiento de historias avanzadas:
+  - Dashboard gerencial BI (HU-09)
+  - Modelo predictivo de insumos IA (HU-10)
+• Deuda técnica de pruebas: 0% (281 tests frontend integrados en PR #10)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Completadas en desarrollo (HECHO / Done): 16 tareas (100% de avance técnico)
+• [T-15] Sprint Planning 2 y refinamiento técnico
 • [T-16] Modelo SQLAlchemy piezas y consumos
 • [T-17] Modelo SQLAlchemy auditoría de pagos
-• [T-19] Endpoints REST piezas de lote
+• [T-19] Endpoints REST piezas de lote en FastAPI
 • [T-20] Lógica de consumos y ganancia neta
-• [T-21] Servicio auditoría de pagos y candado
+• [T-21] Servicio auditoría de pagos y candado digital
 • [T-22] Endpoint Venta Rápida express
 • [T-23] UI Angular piezas de lote y consumos
 • [T-24] UI Angular venta rápida y auditoría
 • [T-25] Migración oficial Alembic (PR #3)
-• [T-26] Pruebas backend pytest (93 pasadas)
+• [T-26] Pruebas backend pytest (93 pasadas al 100%)
 • [T-27] Correcciones documentación SEM04
-• [T-29/T-30] Pipeline CI/CD GitHub Actions + VPS (PR #4 y #5)
-• [T-31/T-32] Nginx reverse proxy y fix test runner
-• [T-36] Acta de Aceptación formal de Entregables
-Porcentaje de avance técnico: 93.8% (15 de 16)
-Story Points devengados en el ciclo: 26 SP
-Estado: Aceptado y Conforme en Sprint Review</t>
+• [T-29 / T-30] Pipeline CI/CD en GitHub Actions y VPS (PR #4 y #5)
+• [T-31 / T-32] Nginx reverse proxy y fix target Vitest
+• [T-35] Pruebas unitarias Angular con Vitest (281 pasadas al 100% en PR #10)
+• [T-36] Generación del Acta de Aceptación de Entregables
+TOTAL PRUEBAS AUTOMATIZADAS DEL PROYECTO: 374 tests (93 backend + 281 frontend) pasando al 100%</t>
         </is>
       </c>
     </row>

--- a/docs/entregables/SEM05/SCRUM_DIARIO.xlsx
+++ b/docs/entregables/SEM05/SCRUM_DIARIO.xlsx
@@ -960,7 +960,7 @@
 • [T-32] Target de test en angular.json corregido; npm test validado en CI. (Gerardo)
 • [T-33] Runbook de despliegue y plantillas VPS versionados en docs/despliegue/. (Gerardo)
 • [T-34] Informe de Estado de Semana 4 subsanado al 100% conforme a observaciones de clase 5. (Gerardo)
-• [T-35] Suite exhaustiva de pruebas unitarias frontend completada: 281 pruebas pasando al 100% en 35 suites (mergeado a main vía PR #10). (Diego, Estibb)</t>
+• [T-35] Suite exhaustiva de pruebas unitarias frontend completada: 282 pruebas pasando al 100% en 35 suites (mergeado a main vía PR #10 y PR #11). (Diego, Estibb)</t>
         </is>
       </c>
     </row>
@@ -969,37 +969,35 @@
         <is>
           <t>Sprint 2 — Día 6
 (Sábado 26/09/2026)
-Sprint Review, Cobertura Integral y Acta de Entrega</t>
+Sustentación T1 y Aceptación en Taller</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>• [T-36] Generación del Acta de Aceptación de Entregables formal para entrega al cliente. (Gerardo)
-• [T-37] Presentación del incremento funcional de Sprint 2 (Software + CI/CD + 374 tests) ante el docente en clase. (Equipo)
-• [T-38] Reunión técnica presencial post-clase con Marcell Vásquez Loje para entrega y suscripción del Acta. (Equipo)
-• [T-39] Consolidación de métricas de calidad y verificación de 0% deuda técnica en pruebas automatizadas. (Equipo)</t>
+          <t>• [T-36] Sustentación del portafolio y entregables de T1 en sesión de clase universitaria ante docente asesor. (Equipo)
+• [T-37] Reunión presencial en taller de Impresos Trujillo E.I.R.L. con Juan Carlos Plasencia y Marcell Vásquez. (Equipo)
+• [T-38] Demostración técnica del incremento de Sprint 2 (Caja con candado digital, bobinas UV DTF, ventas express, CI/CD en VPS). (Equipo)
+• [T-39] Formalización y suscripción del Acta de Aceptación de Entregables AAE-01. (Equipo)</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Cero impedimentos bloqueantes al cierre de la semana.</t>
+          <t>Sin impedimentos; sustentación académica y reunión presencial en taller ejecutadas satisfactoriamente en sus horarios programados del sábado 26/09.</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>• [T-36] Generación formal del Acta de Aceptación de Entregables en Word, PDF y Markdown. (Gerardo)
-• [T-37] Sprint Review y demostración de avances en sesión de clase. (Equipo)
-• [T-38] Reunión técnica presencial en taller de Impresos Trujillo E.I.R.L. (Equipo)
-• [T-39] Ejecución de suite combinada: 93 pruebas backend pytest + 281 pruebas frontend Vitest = 374 pruebas en verde. (Equipo)</t>
+          <t>• [T-36] Exposición y sustentación del portafolio T1 en sesión de clase. (Equipo)
+• [T-37 / T-38] Demostración funcional en vivo en taller para la gerencia de la empresa. (Equipo)
+• [T-39] Suscripción del Acta de Aceptación de Entregables AAE-01 con firmas y sellos de gerencia. (Equipo)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>• [T-36] Acta de Aceptación de Entregables formalizada y lista para firmas físicas en reunión del 26/09/2026. (Gerardo)
-• [T-37] Incremento de Sprint 2 (Inventario continuo de bobinas, venta rápida express, auditoría de pagos, CI/CD y 374 tests) sustentado exitosamente ante el docente. (Equipo)
-• [T-38] Acta de Aceptación suscrita por la Gerente Marcell Vásquez Loje al cierre de la jornada. (Equipo)
-• [T-39] Cobertura automatizada integral verificada (0 fallos en backend y frontend). Deuda técnica de pruebas eliminada al 100%. (Equipo)
-• Cierre formal del Sprint 2 con el 100% de criterios de DoD cumplidos (HU-02, HU-03, HU-04, HU-07, HU-08). (Equipo)</t>
+          <t>• [T-36] Sustentación de portafolio T1 completada satisfactoriamente en clase universitaria ante docente asesor. (Equipo)
+• [T-37 / T-38] Reunión técnica en taller completada exitosamente con Juan Carlos Plasencia (Gerente General) y Marcell Vásquez (Product Owner); incremento aprobado al 100%. (Equipo)
+• [T-39] Acta de Aceptación de Entregables (AAE-01) suscrita formalmente por gerencia el sábado 26/09/2026. (Equipo)
+• Cierre formal del hito de Evaluación T1 / Sprint 2 con 100% de criterios DoD cumplidos y semáforo verde. (Equipo)</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1035,7 @@
 • Refinamiento de historias avanzadas:
   - Dashboard gerencial BI (HU-09)
   - Modelo predictivo de insumos IA (HU-10)
-• Deuda técnica de pruebas: 0% (281 tests frontend integrados en PR #10)</t>
+• Deuda técnica de pruebas: 0% (282 tests frontend integrados en PR #10 y PR #11)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -1057,9 +1055,9 @@
 • [T-27] Correcciones documentación SEM04
 • [T-29 / T-30] Pipeline CI/CD en GitHub Actions y VPS (PR #4 y #5)
 • [T-31 / T-32] Nginx reverse proxy y fix target Vitest
-• [T-35] Pruebas unitarias Angular con Vitest (281 pasadas al 100% en PR #10)
+• [T-35] Pruebas unitarias Angular con Vitest (282 pasadas al 100% en PR #10 y PR #11)
 • [T-36] Generación del Acta de Aceptación de Entregables
-TOTAL PRUEBAS AUTOMATIZADAS DEL PROYECTO: 374 tests (93 backend + 281 frontend) pasando al 100%</t>
+TOTAL PRUEBAS AUTOMATIZADAS DEL PROYECTO: 375 tests (93 backend + 282 frontend) pasando al 100%</t>
         </is>
       </c>
     </row>
